--- a/llegadasTarde/datosEntrada/Document.xlsx
+++ b/llegadasTarde/datosEntrada/Document.xlsx
@@ -84,7 +84,7 @@
     <t>Página: 1 de 59</t>
   </si>
   <si>
-    <t xml:space="preserve">Desde: 01/01/2026  |  Hasta: 13/02/2026</t>
+    <t xml:space="preserve">Desde: 01/01/2026  |  Hasta: 17/02/2026</t>
   </si>
   <si>
     <t>Estudiante - Identificación</t>
@@ -105,7 +105,7 @@
     <t>www.q10.com</t>
   </si>
   <si>
-    <t>Fecha de impresión: 13/02/2026</t>
+    <t>Fecha de impresión: 17/02/2026</t>
   </si>
   <si>
     <t>Página: 2 de 59</t>
@@ -6271,10 +6271,12 @@
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
+      <c r="I37" s="14">
+        <v>46066.653182870366</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" ht="185.25" customHeight="1"/>
     <row r="39" ht="0.75" customHeight="1"/>
@@ -9719,10 +9721,12 @@
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="I32" s="14">
+        <v>46066.656631944439</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" ht="264" customHeight="1"/>
     <row r="34" ht="0.75" customHeight="1"/>
@@ -11021,10 +11025,12 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="I35" s="14">
+        <v>46066.654328703698</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" ht="216.75" customHeight="1"/>
     <row r="37" ht="0.75" customHeight="1"/>
@@ -12042,10 +12048,12 @@
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
+      <c r="I40" s="14">
+        <v>46066.655775462961</v>
+      </c>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
     </row>
     <row r="41" ht="137.25" customHeight="1"/>
     <row r="42" ht="0.75" customHeight="1"/>
@@ -13284,10 +13292,12 @@
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
+      <c r="I33" s="14">
+        <v>46066.665324074071</v>
+      </c>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" ht="248.25" customHeight="1"/>
     <row r="35" ht="0.75" customHeight="1"/>
@@ -14199,10 +14209,12 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="I35" s="14">
+        <v>46066.647638888884</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" ht="216.75" customHeight="1"/>
     <row r="37" ht="0.75" customHeight="1"/>
@@ -15645,10 +15657,12 @@
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
+      <c r="I36" s="14">
+        <v>46066.651087962964</v>
+      </c>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" ht="201" customHeight="1"/>
     <row r="38" ht="0.75" customHeight="1"/>
@@ -16985,10 +16999,12 @@
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
+      <c r="I34" s="14">
+        <v>46066.655393518515</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" ht="232.5" customHeight="1"/>
     <row r="36" ht="0.75" customHeight="1"/>
@@ -17655,10 +17671,12 @@
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
+      <c r="I33" s="14">
+        <v>46066.647581018515</v>
+      </c>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" ht="248.25" customHeight="1"/>
     <row r="35" ht="0.75" customHeight="1"/>
@@ -18362,10 +18380,12 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="I35" s="14">
+        <v>46066.650416666664</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" ht="216.75" customHeight="1"/>
     <row r="37" ht="0.75" customHeight="1"/>
@@ -20055,10 +20075,12 @@
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
+      <c r="I31" s="14">
+        <v>46066.650729166664</v>
+      </c>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
     </row>
     <row r="32" ht="280.5" customHeight="1"/>
     <row r="33" ht="0.75" customHeight="1"/>
@@ -20876,10 +20898,12 @@
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
+      <c r="I41" s="14">
+        <v>46066.655821759254</v>
+      </c>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
     </row>
     <row r="42" ht="121.5" customHeight="1"/>
     <row r="43" ht="0.75" customHeight="1"/>
@@ -23343,10 +23367,12 @@
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="I32" s="14">
+        <v>46066.655462962961</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" ht="264" customHeight="1"/>
     <row r="34" ht="0.75" customHeight="1"/>
@@ -24973,10 +24999,12 @@
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
+      <c r="I34" s="14">
+        <v>46066.650104166663</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" ht="232.5" customHeight="1"/>
     <row r="36" ht="0.75" customHeight="1"/>
@@ -25914,10 +25942,12 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="I35" s="14">
+        <v>46066.670590277776</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" ht="216.75" customHeight="1"/>
     <row r="37" ht="0.75" customHeight="1"/>
@@ -29753,10 +29783,12 @@
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="I32" s="14">
+        <v>46066.656215277777</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" ht="264" customHeight="1"/>
     <row r="34" ht="0.75" customHeight="1"/>
@@ -31586,10 +31618,12 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="I35" s="14">
+        <v>46066.66538194444</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" ht="216.75" customHeight="1"/>
     <row r="37" ht="0.75" customHeight="1"/>
@@ -32527,10 +32561,12 @@
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
+      <c r="I36" s="14">
+        <v>46066.660821759258</v>
+      </c>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" ht="201" customHeight="1"/>
     <row r="38" ht="0.75" customHeight="1"/>
